--- a/history_prices/AUG/prices_07082026.xlsx
+++ b/history_prices/AUG/prices_07082026.xlsx
@@ -13854,6 +13854,110 @@
         </is>
       </c>
     </row>
+    <row r="301" ht="19.2" customHeight="1">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>МАРЖ</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>ДИАС  КАРС ООД</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Diesel EKONOMY</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" s="3" t="n">
+        <v>1.693</v>
+      </c>
+      <c r="H301" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I301" s="2" t="n">
+        <v>1.723</v>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>v.nikolova@gtapetroleum.com</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>bsppbgbspp@gmail.com</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>203918574</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="19.2" customHeight="1">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>0451</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>МАРЖ</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ДИАС  КАРС ООД</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>95 EKONOMY Unleaded</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" s="3" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="H302" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I302" s="2" t="n">
+        <v>1.489</v>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>v.nikolova@gtapetroleum.com</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>bsppbgbspp@gmail.com</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>203918574</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
